--- a/data/Almacen MB52/Base MB52 379.XLSX
+++ b/data/Almacen MB52/Base MB52 379.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\04.MilicicCon\Abastecimiento\08. Compras para Obra\REPORTES\MM\Almacen MB52\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B74949E-F783-4CA6-B4F8-EFA349E78D49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBD41B22-BB42-4B3B-A182-BEFC6879C1C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="57">
   <si>
     <t/>
   </si>
@@ -148,16 +148,49 @@
     <t>1016727</t>
   </si>
   <si>
-    <t>1036861</t>
-  </si>
-  <si>
     <t>1040975</t>
   </si>
   <si>
-    <t>1041585</t>
-  </si>
-  <si>
     <t>1041725</t>
+  </si>
+  <si>
+    <t>1001672</t>
+  </si>
+  <si>
+    <t>1001682</t>
+  </si>
+  <si>
+    <t>1001701</t>
+  </si>
+  <si>
+    <t>1001707</t>
+  </si>
+  <si>
+    <t>1001708</t>
+  </si>
+  <si>
+    <t>1001716</t>
+  </si>
+  <si>
+    <t>1001895</t>
+  </si>
+  <si>
+    <t>1009471</t>
+  </si>
+  <si>
+    <t>1009481</t>
+  </si>
+  <si>
+    <t>1015947</t>
+  </si>
+  <si>
+    <t>1016894</t>
+  </si>
+  <si>
+    <t>1017031</t>
+  </si>
+  <si>
+    <t>1056086</t>
   </si>
 </sst>
 </file>
@@ -583,7 +616,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R28"/>
+  <dimension ref="A1:R41"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.77734375" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
@@ -662,7 +695,7 @@
     </row>
     <row r="2" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>22</v>
@@ -677,13 +710,13 @@
         <v>1</v>
       </c>
       <c r="F2" s="4">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>2</v>
       </c>
       <c r="H2" s="5">
-        <v>37607.67</v>
+        <v>105393.07</v>
       </c>
       <c r="I2" s="4">
         <v>0</v>
@@ -718,7 +751,7 @@
     </row>
     <row r="3" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>22</v>
@@ -733,13 +766,13 @@
         <v>1</v>
       </c>
       <c r="F3" s="4">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>2</v>
       </c>
       <c r="H3" s="5">
-        <v>39981.64</v>
+        <v>182176.2</v>
       </c>
       <c r="I3" s="4">
         <v>0</v>
@@ -774,7 +807,7 @@
     </row>
     <row r="4" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>22</v>
@@ -789,13 +822,13 @@
         <v>1</v>
       </c>
       <c r="F4" s="4">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>2</v>
       </c>
       <c r="H4" s="5">
-        <v>18938.669999999998</v>
+        <v>13912.71</v>
       </c>
       <c r="I4" s="4">
         <v>0</v>
@@ -830,7 +863,7 @@
     </row>
     <row r="5" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>22</v>
@@ -845,13 +878,13 @@
         <v>1</v>
       </c>
       <c r="F5" s="4">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>2</v>
       </c>
       <c r="H5" s="5">
-        <v>68294.47</v>
+        <v>361165.6</v>
       </c>
       <c r="I5" s="4">
         <v>0</v>
@@ -886,7 +919,7 @@
     </row>
     <row r="6" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>22</v>
@@ -901,13 +934,13 @@
         <v>1</v>
       </c>
       <c r="F6" s="4">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>2</v>
       </c>
       <c r="H6" s="5">
-        <v>147408.47</v>
+        <v>9470.2099999999991</v>
       </c>
       <c r="I6" s="4">
         <v>0</v>
@@ -942,7 +975,7 @@
     </row>
     <row r="7" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>22</v>
@@ -957,13 +990,13 @@
         <v>1</v>
       </c>
       <c r="F7" s="4">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>2</v>
       </c>
       <c r="H7" s="5">
-        <v>54240.28</v>
+        <v>29867.57</v>
       </c>
       <c r="I7" s="4">
         <v>0</v>
@@ -998,7 +1031,7 @@
     </row>
     <row r="8" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>22</v>
@@ -1013,13 +1046,13 @@
         <v>1</v>
       </c>
       <c r="F8" s="4">
-        <v>2</v>
+        <v>47</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>2</v>
       </c>
       <c r="H8" s="5">
-        <v>57794.080000000002</v>
+        <v>22018.15</v>
       </c>
       <c r="I8" s="4">
         <v>0</v>
@@ -1054,7 +1087,7 @@
     </row>
     <row r="9" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>22</v>
@@ -1069,13 +1102,13 @@
         <v>1</v>
       </c>
       <c r="F9" s="4">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>2</v>
       </c>
       <c r="H9" s="5">
-        <v>206590.8</v>
+        <v>37607.67</v>
       </c>
       <c r="I9" s="4">
         <v>0</v>
@@ -1110,7 +1143,7 @@
     </row>
     <row r="10" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>22</v>
@@ -1125,13 +1158,13 @@
         <v>1</v>
       </c>
       <c r="F10" s="4">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>2</v>
       </c>
       <c r="H10" s="5">
-        <v>96814.36</v>
+        <v>16762.060000000001</v>
       </c>
       <c r="I10" s="4">
         <v>0</v>
@@ -1166,7 +1199,7 @@
     </row>
     <row r="11" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>22</v>
@@ -1181,13 +1214,13 @@
         <v>1</v>
       </c>
       <c r="F11" s="4">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>2</v>
       </c>
       <c r="H11" s="5">
-        <v>90737.21</v>
+        <v>39981.64</v>
       </c>
       <c r="I11" s="4">
         <v>0</v>
@@ -1222,7 +1255,7 @@
     </row>
     <row r="12" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>22</v>
@@ -1237,13 +1270,13 @@
         <v>1</v>
       </c>
       <c r="F12" s="4">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>2</v>
       </c>
       <c r="H12" s="5">
-        <v>30245.74</v>
+        <v>18938.669999999998</v>
       </c>
       <c r="I12" s="4">
         <v>0</v>
@@ -1278,7 +1311,7 @@
     </row>
     <row r="13" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>22</v>
@@ -1293,13 +1326,13 @@
         <v>1</v>
       </c>
       <c r="F13" s="4">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>2</v>
       </c>
       <c r="H13" s="5">
-        <v>12294.06</v>
+        <v>68294.47</v>
       </c>
       <c r="I13" s="4">
         <v>0</v>
@@ -1334,7 +1367,7 @@
     </row>
     <row r="14" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>22</v>
@@ -1349,13 +1382,13 @@
         <v>1</v>
       </c>
       <c r="F14" s="4">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>2</v>
       </c>
       <c r="H14" s="5">
-        <v>159822.76</v>
+        <v>147408.47</v>
       </c>
       <c r="I14" s="4">
         <v>0</v>
@@ -1390,7 +1423,7 @@
     </row>
     <row r="15" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>22</v>
@@ -1405,13 +1438,13 @@
         <v>1</v>
       </c>
       <c r="F15" s="4">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>2</v>
       </c>
       <c r="H15" s="5">
-        <v>0</v>
+        <v>54240.28</v>
       </c>
       <c r="I15" s="4">
         <v>0</v>
@@ -1446,7 +1479,7 @@
     </row>
     <row r="16" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>22</v>
@@ -1461,13 +1494,13 @@
         <v>1</v>
       </c>
       <c r="F16" s="4">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>2</v>
       </c>
       <c r="H16" s="5">
-        <v>51616.13</v>
+        <v>40045.599999999999</v>
       </c>
       <c r="I16" s="4">
         <v>0</v>
@@ -1502,7 +1535,7 @@
     </row>
     <row r="17" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>22</v>
@@ -1517,13 +1550,13 @@
         <v>1</v>
       </c>
       <c r="F17" s="4">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>2</v>
       </c>
       <c r="H17" s="5">
-        <v>260096.84</v>
+        <v>24544.080000000002</v>
       </c>
       <c r="I17" s="4">
         <v>0</v>
@@ -1558,7 +1591,7 @@
     </row>
     <row r="18" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>22</v>
@@ -1573,13 +1606,13 @@
         <v>1</v>
       </c>
       <c r="F18" s="4">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>2</v>
       </c>
       <c r="H18" s="5">
-        <v>130616.62</v>
+        <v>57794.080000000002</v>
       </c>
       <c r="I18" s="4">
         <v>0</v>
@@ -1614,7 +1647,7 @@
     </row>
     <row r="19" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>22</v>
@@ -1629,13 +1662,13 @@
         <v>1</v>
       </c>
       <c r="F19" s="4">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>2</v>
       </c>
       <c r="H19" s="5">
-        <v>34587.32</v>
+        <v>206590.8</v>
       </c>
       <c r="I19" s="4">
         <v>0</v>
@@ -1670,7 +1703,7 @@
     </row>
     <row r="20" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>22</v>
@@ -1691,7 +1724,7 @@
         <v>2</v>
       </c>
       <c r="H20" s="5">
-        <v>764268.39</v>
+        <v>96814.36</v>
       </c>
       <c r="I20" s="4">
         <v>0</v>
@@ -1726,7 +1759,7 @@
     </row>
     <row r="21" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>22</v>
@@ -1741,13 +1774,13 @@
         <v>1</v>
       </c>
       <c r="F21" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>2</v>
       </c>
       <c r="H21" s="5">
-        <v>175125.81</v>
+        <v>90737.21</v>
       </c>
       <c r="I21" s="4">
         <v>0</v>
@@ -1782,7 +1815,7 @@
     </row>
     <row r="22" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>22</v>
@@ -1803,7 +1836,7 @@
         <v>2</v>
       </c>
       <c r="H22" s="5">
-        <v>181460.47</v>
+        <v>30245.74</v>
       </c>
       <c r="I22" s="4">
         <v>0</v>
@@ -1838,7 +1871,7 @@
     </row>
     <row r="23" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>33</v>
+        <v>52</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>22</v>
@@ -1853,13 +1886,13 @@
         <v>1</v>
       </c>
       <c r="F23" s="4">
-        <v>20</v>
+        <v>49</v>
       </c>
       <c r="G23" s="3" t="s">
         <v>2</v>
       </c>
       <c r="H23" s="5">
-        <v>220641.71</v>
+        <v>64931.43</v>
       </c>
       <c r="I23" s="4">
         <v>0</v>
@@ -1894,7 +1927,7 @@
     </row>
     <row r="24" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>22</v>
@@ -1909,13 +1942,13 @@
         <v>1</v>
       </c>
       <c r="F24" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>2</v>
       </c>
       <c r="H24" s="5">
-        <v>4573711.41</v>
+        <v>12294.06</v>
       </c>
       <c r="I24" s="4">
         <v>0</v>
@@ -1950,7 +1983,7 @@
     </row>
     <row r="25" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>43</v>
+        <v>21</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>22</v>
@@ -1965,13 +1998,13 @@
         <v>1</v>
       </c>
       <c r="F25" s="4">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="G25" s="3" t="s">
         <v>2</v>
       </c>
       <c r="H25" s="5">
-        <v>158893.14000000001</v>
+        <v>159822.76</v>
       </c>
       <c r="I25" s="4">
         <v>0</v>
@@ -2006,7 +2039,7 @@
     </row>
     <row r="26" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>22</v>
@@ -2021,13 +2054,13 @@
         <v>1</v>
       </c>
       <c r="F26" s="4">
-        <v>1</v>
+        <v>43</v>
       </c>
       <c r="G26" s="3" t="s">
         <v>2</v>
       </c>
       <c r="H26" s="5">
-        <v>1065145.93</v>
+        <v>0</v>
       </c>
       <c r="I26" s="4">
         <v>0</v>
@@ -2062,7 +2095,7 @@
     </row>
     <row r="27" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>22</v>
@@ -2077,98 +2110,826 @@
         <v>1</v>
       </c>
       <c r="F27" s="4">
+        <v>7</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="H27" s="5">
+        <v>0</v>
+      </c>
+      <c r="I27" s="4">
+        <v>0</v>
+      </c>
+      <c r="J27" s="5">
+        <v>0</v>
+      </c>
+      <c r="K27" s="4">
+        <v>0</v>
+      </c>
+      <c r="L27" s="5">
+        <v>0</v>
+      </c>
+      <c r="M27" s="4">
+        <v>0</v>
+      </c>
+      <c r="N27" s="5">
+        <v>0</v>
+      </c>
+      <c r="O27" s="4">
+        <v>0</v>
+      </c>
+      <c r="P27" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q27" s="4">
+        <v>0</v>
+      </c>
+      <c r="R27" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
+      <c r="A28" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F28" s="4">
+        <v>1</v>
+      </c>
+      <c r="G28" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="H28" s="5">
+        <v>51616.13</v>
+      </c>
+      <c r="I28" s="4">
+        <v>0</v>
+      </c>
+      <c r="J28" s="5">
+        <v>0</v>
+      </c>
+      <c r="K28" s="4">
+        <v>0</v>
+      </c>
+      <c r="L28" s="5">
+        <v>0</v>
+      </c>
+      <c r="M28" s="4">
+        <v>0</v>
+      </c>
+      <c r="N28" s="5">
+        <v>0</v>
+      </c>
+      <c r="O28" s="4">
+        <v>0</v>
+      </c>
+      <c r="P28" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="4">
+        <v>0</v>
+      </c>
+      <c r="R28" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
+      <c r="A29" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F29" s="4">
         <v>4</v>
       </c>
-      <c r="G27" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="H27" s="5">
-        <v>753841.77</v>
-      </c>
-      <c r="I27" s="4">
-        <v>0</v>
-      </c>
-      <c r="J27" s="5">
-        <v>0</v>
-      </c>
-      <c r="K27" s="4">
-        <v>0</v>
-      </c>
-      <c r="L27" s="5">
-        <v>0</v>
-      </c>
-      <c r="M27" s="4">
-        <v>0</v>
-      </c>
-      <c r="N27" s="5">
-        <v>0</v>
-      </c>
-      <c r="O27" s="4">
-        <v>0</v>
-      </c>
-      <c r="P27" s="5">
-        <v>0</v>
-      </c>
-      <c r="Q27" s="4">
-        <v>0</v>
-      </c>
-      <c r="R27" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
-      <c r="A28" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="B28" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="C28" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="D28" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="E28" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="F28" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="G28" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="H28" s="7">
-        <v>9390775.75</v>
-      </c>
-      <c r="I28" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="J28" s="7">
-        <v>0</v>
-      </c>
-      <c r="K28" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="L28" s="7">
-        <v>0</v>
-      </c>
-      <c r="M28" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="N28" s="7">
-        <v>0</v>
-      </c>
-      <c r="O28" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="P28" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q28" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="R28" s="7">
+      <c r="G29" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="H29" s="5">
+        <v>208077.47</v>
+      </c>
+      <c r="I29" s="4">
+        <v>0</v>
+      </c>
+      <c r="J29" s="5">
+        <v>0</v>
+      </c>
+      <c r="K29" s="4">
+        <v>0</v>
+      </c>
+      <c r="L29" s="5">
+        <v>0</v>
+      </c>
+      <c r="M29" s="4">
+        <v>0</v>
+      </c>
+      <c r="N29" s="5">
+        <v>0</v>
+      </c>
+      <c r="O29" s="4">
+        <v>0</v>
+      </c>
+      <c r="P29" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="4">
+        <v>0</v>
+      </c>
+      <c r="R29" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
+      <c r="A30" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F30" s="4">
+        <v>6</v>
+      </c>
+      <c r="G30" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="H30" s="5">
+        <v>111957.1</v>
+      </c>
+      <c r="I30" s="4">
+        <v>0</v>
+      </c>
+      <c r="J30" s="5">
+        <v>0</v>
+      </c>
+      <c r="K30" s="4">
+        <v>0</v>
+      </c>
+      <c r="L30" s="5">
+        <v>0</v>
+      </c>
+      <c r="M30" s="4">
+        <v>0</v>
+      </c>
+      <c r="N30" s="5">
+        <v>0</v>
+      </c>
+      <c r="O30" s="4">
+        <v>0</v>
+      </c>
+      <c r="P30" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="4">
+        <v>0</v>
+      </c>
+      <c r="R30" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
+      <c r="A31" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F31" s="4">
+        <v>1</v>
+      </c>
+      <c r="G31" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="H31" s="5">
+        <v>17293.66</v>
+      </c>
+      <c r="I31" s="4">
+        <v>0</v>
+      </c>
+      <c r="J31" s="5">
+        <v>0</v>
+      </c>
+      <c r="K31" s="4">
+        <v>0</v>
+      </c>
+      <c r="L31" s="5">
+        <v>0</v>
+      </c>
+      <c r="M31" s="4">
+        <v>0</v>
+      </c>
+      <c r="N31" s="5">
+        <v>0</v>
+      </c>
+      <c r="O31" s="4">
+        <v>0</v>
+      </c>
+      <c r="P31" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="4">
+        <v>0</v>
+      </c>
+      <c r="R31" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
+      <c r="A32" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F32" s="4">
+        <v>27</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="H32" s="5">
+        <v>229469.75</v>
+      </c>
+      <c r="I32" s="4">
+        <v>0</v>
+      </c>
+      <c r="J32" s="5">
+        <v>0</v>
+      </c>
+      <c r="K32" s="4">
+        <v>0</v>
+      </c>
+      <c r="L32" s="5">
+        <v>0</v>
+      </c>
+      <c r="M32" s="4">
+        <v>0</v>
+      </c>
+      <c r="N32" s="5">
+        <v>0</v>
+      </c>
+      <c r="O32" s="4">
+        <v>0</v>
+      </c>
+      <c r="P32" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="4">
+        <v>0</v>
+      </c>
+      <c r="R32" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
+      <c r="A33" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F33" s="4">
+        <v>20</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="H33" s="5">
+        <v>139140.21</v>
+      </c>
+      <c r="I33" s="4">
+        <v>0</v>
+      </c>
+      <c r="J33" s="5">
+        <v>0</v>
+      </c>
+      <c r="K33" s="4">
+        <v>0</v>
+      </c>
+      <c r="L33" s="5">
+        <v>0</v>
+      </c>
+      <c r="M33" s="4">
+        <v>0</v>
+      </c>
+      <c r="N33" s="5">
+        <v>0</v>
+      </c>
+      <c r="O33" s="4">
+        <v>0</v>
+      </c>
+      <c r="P33" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q33" s="4">
+        <v>0</v>
+      </c>
+      <c r="R33" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
+      <c r="A34" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F34" s="4">
+        <v>2</v>
+      </c>
+      <c r="G34" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="H34" s="5">
+        <v>764268.39</v>
+      </c>
+      <c r="I34" s="4">
+        <v>0</v>
+      </c>
+      <c r="J34" s="5">
+        <v>0</v>
+      </c>
+      <c r="K34" s="4">
+        <v>0</v>
+      </c>
+      <c r="L34" s="5">
+        <v>0</v>
+      </c>
+      <c r="M34" s="4">
+        <v>0</v>
+      </c>
+      <c r="N34" s="5">
+        <v>0</v>
+      </c>
+      <c r="O34" s="4">
+        <v>0</v>
+      </c>
+      <c r="P34" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="4">
+        <v>0</v>
+      </c>
+      <c r="R34" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
+      <c r="A35" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F35" s="4">
+        <v>1</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="H35" s="5">
+        <v>175125.81</v>
+      </c>
+      <c r="I35" s="4">
+        <v>0</v>
+      </c>
+      <c r="J35" s="5">
+        <v>0</v>
+      </c>
+      <c r="K35" s="4">
+        <v>0</v>
+      </c>
+      <c r="L35" s="5">
+        <v>0</v>
+      </c>
+      <c r="M35" s="4">
+        <v>0</v>
+      </c>
+      <c r="N35" s="5">
+        <v>0</v>
+      </c>
+      <c r="O35" s="4">
+        <v>0</v>
+      </c>
+      <c r="P35" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q35" s="4">
+        <v>0</v>
+      </c>
+      <c r="R35" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
+      <c r="A36" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F36" s="4">
+        <v>1</v>
+      </c>
+      <c r="G36" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="H36" s="5">
+        <v>181460.47</v>
+      </c>
+      <c r="I36" s="4">
+        <v>0</v>
+      </c>
+      <c r="J36" s="5">
+        <v>0</v>
+      </c>
+      <c r="K36" s="4">
+        <v>0</v>
+      </c>
+      <c r="L36" s="5">
+        <v>0</v>
+      </c>
+      <c r="M36" s="4">
+        <v>0</v>
+      </c>
+      <c r="N36" s="5">
+        <v>0</v>
+      </c>
+      <c r="O36" s="4">
+        <v>0</v>
+      </c>
+      <c r="P36" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q36" s="4">
+        <v>0</v>
+      </c>
+      <c r="R36" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
+      <c r="A37" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F37" s="4">
+        <v>20</v>
+      </c>
+      <c r="G37" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="H37" s="5">
+        <v>220641.71</v>
+      </c>
+      <c r="I37" s="4">
+        <v>0</v>
+      </c>
+      <c r="J37" s="5">
+        <v>0</v>
+      </c>
+      <c r="K37" s="4">
+        <v>0</v>
+      </c>
+      <c r="L37" s="5">
+        <v>0</v>
+      </c>
+      <c r="M37" s="4">
+        <v>0</v>
+      </c>
+      <c r="N37" s="5">
+        <v>0</v>
+      </c>
+      <c r="O37" s="4">
+        <v>0</v>
+      </c>
+      <c r="P37" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q37" s="4">
+        <v>0</v>
+      </c>
+      <c r="R37" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
+      <c r="A38" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F38" s="4">
+        <v>1</v>
+      </c>
+      <c r="G38" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="H38" s="5">
+        <v>158893.14000000001</v>
+      </c>
+      <c r="I38" s="4">
+        <v>0</v>
+      </c>
+      <c r="J38" s="5">
+        <v>0</v>
+      </c>
+      <c r="K38" s="4">
+        <v>0</v>
+      </c>
+      <c r="L38" s="5">
+        <v>0</v>
+      </c>
+      <c r="M38" s="4">
+        <v>0</v>
+      </c>
+      <c r="N38" s="5">
+        <v>0</v>
+      </c>
+      <c r="O38" s="4">
+        <v>0</v>
+      </c>
+      <c r="P38" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q38" s="4">
+        <v>0</v>
+      </c>
+      <c r="R38" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
+      <c r="A39" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F39" s="4">
+        <v>2</v>
+      </c>
+      <c r="G39" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="H39" s="5">
+        <v>376920.88</v>
+      </c>
+      <c r="I39" s="4">
+        <v>0</v>
+      </c>
+      <c r="J39" s="5">
+        <v>0</v>
+      </c>
+      <c r="K39" s="4">
+        <v>0</v>
+      </c>
+      <c r="L39" s="5">
+        <v>0</v>
+      </c>
+      <c r="M39" s="4">
+        <v>0</v>
+      </c>
+      <c r="N39" s="5">
+        <v>0</v>
+      </c>
+      <c r="O39" s="4">
+        <v>0</v>
+      </c>
+      <c r="P39" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q39" s="4">
+        <v>0</v>
+      </c>
+      <c r="R39" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
+      <c r="A40" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F40" s="4">
+        <v>40</v>
+      </c>
+      <c r="G40" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="H40" s="5">
+        <v>10350.99</v>
+      </c>
+      <c r="I40" s="4">
+        <v>0</v>
+      </c>
+      <c r="J40" s="5">
+        <v>0</v>
+      </c>
+      <c r="K40" s="4">
+        <v>0</v>
+      </c>
+      <c r="L40" s="5">
+        <v>0</v>
+      </c>
+      <c r="M40" s="4">
+        <v>0</v>
+      </c>
+      <c r="N40" s="5">
+        <v>0</v>
+      </c>
+      <c r="O40" s="4">
+        <v>0</v>
+      </c>
+      <c r="P40" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q40" s="4">
+        <v>0</v>
+      </c>
+      <c r="R40" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
+      <c r="A41" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B41" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="C41" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D41" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="E41" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="F41" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="G41" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="H41" s="7">
+        <v>4536272.5999999996</v>
+      </c>
+      <c r="I41" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="J41" s="7">
+        <v>0</v>
+      </c>
+      <c r="K41" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="L41" s="7">
+        <v>0</v>
+      </c>
+      <c r="M41" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="N41" s="7">
+        <v>0</v>
+      </c>
+      <c r="O41" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="P41" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q41" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="R41" s="7">
         <v>0</v>
       </c>
     </row>

--- a/data/Almacen MB52/Base MB52 379.XLSX
+++ b/data/Almacen MB52/Base MB52 379.XLSX
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\04.MilicicCon\Abastecimiento\08. Compras para Obra\REPORTES\MM\Almacen MB52\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\david.benitez\Documents\GitHub\abast-milicic.github.io\data\Almacen MB52\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AB4C968-01A7-406C-B91E-37F7CDE422A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3EC5919-C563-4D6C-B042-D4EA2C04A44B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="452" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="417" uniqueCount="65">
   <si>
     <t/>
   </si>
@@ -148,9 +148,6 @@
     <t>1040975</t>
   </si>
   <si>
-    <t>1041725</t>
-  </si>
-  <si>
     <t>1001672</t>
   </si>
   <si>
@@ -199,12 +196,6 @@
     <t>1001778</t>
   </si>
   <si>
-    <t>1001812</t>
-  </si>
-  <si>
-    <t>1001813</t>
-  </si>
-  <si>
     <t>1004256</t>
   </si>
   <si>
@@ -217,16 +208,13 @@
     <t>1056088</t>
   </si>
   <si>
-    <t>0M00501</t>
-  </si>
-  <si>
-    <t>0M00601</t>
-  </si>
-  <si>
-    <t>0M00701</t>
-  </si>
-  <si>
-    <t>0M00901</t>
+    <t>1003466</t>
+  </si>
+  <si>
+    <t>1016479</t>
+  </si>
+  <si>
+    <t>1016480</t>
   </si>
 </sst>
 </file>
@@ -634,7 +622,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S62"/>
+  <dimension ref="A1:S57"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.77734375" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
@@ -667,7 +655,7 @@
         <v>5</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E1" s="6" t="s">
         <v>6</v>
@@ -703,7 +691,7 @@
         <v>16</v>
       </c>
       <c r="P1" s="6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="Q1" s="6" t="s">
         <v>17</v>
@@ -717,7 +705,7 @@
     </row>
     <row r="2" spans="1:19" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>21</v>
@@ -776,7 +764,7 @@
     </row>
     <row r="3" spans="1:19" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>21</v>
@@ -794,13 +782,13 @@
         <v>1</v>
       </c>
       <c r="G3" s="2">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="I3" s="3">
-        <v>569300.62</v>
+        <v>561709.94999999995</v>
       </c>
       <c r="J3" s="2">
         <v>0</v>
@@ -853,13 +841,13 @@
         <v>1</v>
       </c>
       <c r="G4" s="2">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="H4" s="1" t="s">
         <v>2</v>
       </c>
       <c r="I4" s="3">
-        <v>166994.85</v>
+        <v>13912.71</v>
       </c>
       <c r="J4" s="2">
         <v>0</v>
@@ -912,13 +900,13 @@
         <v>1</v>
       </c>
       <c r="G5" s="2">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="H5" s="1" t="s">
         <v>2</v>
       </c>
       <c r="I5" s="3">
-        <v>13912.71</v>
+        <v>325049.03999999998</v>
       </c>
       <c r="J5" s="2">
         <v>0</v>
@@ -971,13 +959,13 @@
         <v>1</v>
       </c>
       <c r="G6" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H6" s="1" t="s">
         <v>2</v>
       </c>
       <c r="I6" s="3">
-        <v>361165.6</v>
+        <v>13841.07</v>
       </c>
       <c r="J6" s="2">
         <v>0</v>
@@ -1012,7 +1000,7 @@
     </row>
     <row r="7" spans="1:19" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>21</v>
@@ -1030,13 +1018,13 @@
         <v>1</v>
       </c>
       <c r="G7" s="2">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="H7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="I7" s="3">
-        <v>17483.46</v>
+        <v>8741.73</v>
       </c>
       <c r="J7" s="2">
         <v>0</v>
@@ -1071,7 +1059,7 @@
     </row>
     <row r="8" spans="1:19" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>21</v>
@@ -1089,13 +1077,13 @@
         <v>1</v>
       </c>
       <c r="G8" s="2">
-        <v>12</v>
+        <v>41</v>
       </c>
       <c r="H8" s="1" t="s">
         <v>2</v>
       </c>
       <c r="I8" s="3">
-        <v>8741.73</v>
+        <v>29867.57</v>
       </c>
       <c r="J8" s="2">
         <v>0</v>
@@ -1148,13 +1136,13 @@
         <v>1</v>
       </c>
       <c r="G9" s="2">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="H9" s="1" t="s">
         <v>2</v>
       </c>
       <c r="I9" s="3">
-        <v>29867.57</v>
+        <v>20612.740000000002</v>
       </c>
       <c r="J9" s="2">
         <v>0</v>
@@ -1189,7 +1177,7 @@
     </row>
     <row r="10" spans="1:19" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>21</v>
@@ -1207,13 +1195,13 @@
         <v>1</v>
       </c>
       <c r="G10" s="2">
-        <v>47</v>
+        <v>2</v>
       </c>
       <c r="H10" s="1" t="s">
         <v>2</v>
       </c>
       <c r="I10" s="3">
-        <v>22018.15</v>
+        <v>3760.77</v>
       </c>
       <c r="J10" s="2">
         <v>0</v>
@@ -1307,7 +1295,7 @@
     </row>
     <row r="12" spans="1:19" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>33</v>
+        <v>57</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>21</v>
@@ -1325,13 +1313,13 @@
         <v>1</v>
       </c>
       <c r="G12" s="2">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="H12" s="1" t="s">
         <v>2</v>
       </c>
       <c r="I12" s="3">
-        <v>37607.67</v>
+        <v>58547.26</v>
       </c>
       <c r="J12" s="2">
         <v>0</v>
@@ -1366,7 +1354,7 @@
     </row>
     <row r="13" spans="1:19" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>21</v>
@@ -1384,13 +1372,13 @@
         <v>1</v>
       </c>
       <c r="G13" s="2">
-        <v>50</v>
+        <v>9</v>
       </c>
       <c r="H13" s="1" t="s">
         <v>2</v>
       </c>
       <c r="I13" s="3">
-        <v>86098.91</v>
+        <v>30171.7</v>
       </c>
       <c r="J13" s="2">
         <v>0</v>
@@ -1425,7 +1413,7 @@
     </row>
     <row r="14" spans="1:19" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>59</v>
+        <v>34</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>21</v>
@@ -1443,13 +1431,13 @@
         <v>1</v>
       </c>
       <c r="G14" s="2">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="H14" s="1" t="s">
         <v>2</v>
       </c>
       <c r="I14" s="3">
-        <v>210283.61</v>
+        <v>63148.11</v>
       </c>
       <c r="J14" s="2">
         <v>0</v>
@@ -1484,7 +1472,7 @@
     </row>
     <row r="15" spans="1:19" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>60</v>
+        <v>34</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>21</v>
@@ -1502,13 +1490,13 @@
         <v>1</v>
       </c>
       <c r="G15" s="2">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="H15" s="1" t="s">
         <v>2</v>
       </c>
       <c r="I15" s="3">
-        <v>539342.04</v>
+        <v>29912.26</v>
       </c>
       <c r="J15" s="2">
         <v>0</v>
@@ -1543,7 +1531,7 @@
     </row>
     <row r="16" spans="1:19" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>21</v>
@@ -1561,13 +1549,13 @@
         <v>1</v>
       </c>
       <c r="G16" s="2">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="H16" s="1" t="s">
         <v>2</v>
       </c>
       <c r="I16" s="3">
-        <v>40228.94</v>
+        <v>68294.47</v>
       </c>
       <c r="J16" s="2">
         <v>0</v>
@@ -1602,7 +1590,7 @@
     </row>
     <row r="17" spans="1:19" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>21</v>
@@ -1620,13 +1608,13 @@
         <v>1</v>
       </c>
       <c r="G17" s="2">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="H17" s="1" t="s">
         <v>2</v>
       </c>
       <c r="I17" s="3">
-        <v>16762.060000000001</v>
+        <v>147408.47</v>
       </c>
       <c r="J17" s="2">
         <v>0</v>
@@ -1661,7 +1649,7 @@
     </row>
     <row r="18" spans="1:19" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>34</v>
+        <v>62</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>21</v>
@@ -1679,13 +1667,13 @@
         <v>1</v>
       </c>
       <c r="G18" s="2">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="H18" s="1" t="s">
         <v>2</v>
       </c>
       <c r="I18" s="3">
-        <v>39981.64</v>
+        <v>438919.32</v>
       </c>
       <c r="J18" s="2">
         <v>0</v>
@@ -1720,7 +1708,7 @@
     </row>
     <row r="19" spans="1:19" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>34</v>
+        <v>58</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>21</v>
@@ -1738,13 +1726,13 @@
         <v>1</v>
       </c>
       <c r="G19" s="2">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="H19" s="1" t="s">
         <v>2</v>
       </c>
       <c r="I19" s="3">
-        <v>18938.669999999998</v>
+        <v>43167.8</v>
       </c>
       <c r="J19" s="2">
         <v>0</v>
@@ -1779,7 +1767,7 @@
     </row>
     <row r="20" spans="1:19" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>21</v>
@@ -1797,13 +1785,13 @@
         <v>1</v>
       </c>
       <c r="G20" s="2">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H20" s="1" t="s">
         <v>2</v>
       </c>
       <c r="I20" s="3">
-        <v>68294.47</v>
+        <v>54240.28</v>
       </c>
       <c r="J20" s="2">
         <v>0</v>
@@ -1838,7 +1826,7 @@
     </row>
     <row r="21" spans="1:19" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>21</v>
@@ -1856,13 +1844,13 @@
         <v>1</v>
       </c>
       <c r="G21" s="2">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="H21" s="1" t="s">
         <v>2</v>
       </c>
       <c r="I21" s="3">
-        <v>147408.47</v>
+        <v>12917.94</v>
       </c>
       <c r="J21" s="2">
         <v>0</v>
@@ -1897,7 +1885,7 @@
     </row>
     <row r="22" spans="1:19" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>21</v>
@@ -1915,13 +1903,13 @@
         <v>1</v>
       </c>
       <c r="G22" s="2">
-        <v>3</v>
+        <v>31</v>
       </c>
       <c r="H22" s="1" t="s">
         <v>2</v>
       </c>
       <c r="I22" s="3">
-        <v>129503.39</v>
+        <v>40045.599999999999</v>
       </c>
       <c r="J22" s="2">
         <v>0</v>
@@ -1956,7 +1944,7 @@
     </row>
     <row r="23" spans="1:19" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>28</v>
+        <v>49</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>21</v>
@@ -1974,13 +1962,13 @@
         <v>1</v>
       </c>
       <c r="G23" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H23" s="1" t="s">
         <v>2</v>
       </c>
       <c r="I23" s="3">
-        <v>54240.28</v>
+        <v>24544.080000000002</v>
       </c>
       <c r="J23" s="2">
         <v>0</v>
@@ -2015,7 +2003,7 @@
     </row>
     <row r="24" spans="1:19" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>50</v>
+        <v>23</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>21</v>
@@ -2033,13 +2021,13 @@
         <v>1</v>
       </c>
       <c r="G24" s="2">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="H24" s="1" t="s">
         <v>2</v>
       </c>
       <c r="I24" s="3">
-        <v>12917.94</v>
+        <v>57794.080000000002</v>
       </c>
       <c r="J24" s="2">
         <v>0</v>
@@ -2074,7 +2062,7 @@
     </row>
     <row r="25" spans="1:19" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>50</v>
+        <v>24</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>21</v>
@@ -2092,13 +2080,13 @@
         <v>1</v>
       </c>
       <c r="G25" s="2">
-        <v>31</v>
+        <v>7</v>
       </c>
       <c r="H25" s="1" t="s">
         <v>2</v>
       </c>
       <c r="I25" s="3">
-        <v>40045.599999999999</v>
+        <v>206590.8</v>
       </c>
       <c r="J25" s="2">
         <v>0</v>
@@ -2133,7 +2121,7 @@
     </row>
     <row r="26" spans="1:19" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>21</v>
@@ -2151,13 +2139,13 @@
         <v>1</v>
       </c>
       <c r="G26" s="2">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="H26" s="1" t="s">
         <v>2</v>
       </c>
       <c r="I26" s="3">
-        <v>24544.080000000002</v>
+        <v>96814.36</v>
       </c>
       <c r="J26" s="2">
         <v>0</v>
@@ -2192,7 +2180,7 @@
     </row>
     <row r="27" spans="1:19" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>21</v>
@@ -2210,13 +2198,13 @@
         <v>1</v>
       </c>
       <c r="G27" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H27" s="1" t="s">
         <v>2</v>
       </c>
       <c r="I27" s="3">
-        <v>57794.080000000002</v>
+        <v>90737.21</v>
       </c>
       <c r="J27" s="2">
         <v>0</v>
@@ -2251,7 +2239,7 @@
     </row>
     <row r="28" spans="1:19" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>21</v>
@@ -2269,13 +2257,13 @@
         <v>1</v>
       </c>
       <c r="G28" s="2">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="H28" s="1" t="s">
         <v>2</v>
       </c>
       <c r="I28" s="3">
-        <v>206590.8</v>
+        <v>30245.74</v>
       </c>
       <c r="J28" s="2">
         <v>0</v>
@@ -2310,7 +2298,7 @@
     </row>
     <row r="29" spans="1:19" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>21</v>
@@ -2328,13 +2316,13 @@
         <v>1</v>
       </c>
       <c r="G29" s="2">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="H29" s="1" t="s">
         <v>2</v>
       </c>
       <c r="I29" s="3">
-        <v>96814.36</v>
+        <v>26502.63</v>
       </c>
       <c r="J29" s="2">
         <v>0</v>
@@ -2369,7 +2357,7 @@
     </row>
     <row r="30" spans="1:19" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>21</v>
@@ -2387,13 +2375,13 @@
         <v>1</v>
       </c>
       <c r="G30" s="2">
-        <v>3</v>
+        <v>49</v>
       </c>
       <c r="H30" s="1" t="s">
         <v>2</v>
       </c>
       <c r="I30" s="3">
-        <v>90737.21</v>
+        <v>64931.44</v>
       </c>
       <c r="J30" s="2">
         <v>0</v>
@@ -2428,7 +2416,7 @@
     </row>
     <row r="31" spans="1:19" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>21</v>
@@ -2446,13 +2434,13 @@
         <v>1</v>
       </c>
       <c r="G31" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H31" s="1" t="s">
         <v>2</v>
       </c>
       <c r="I31" s="3">
-        <v>30245.74</v>
+        <v>12294.06</v>
       </c>
       <c r="J31" s="2">
         <v>0</v>
@@ -2487,7 +2475,7 @@
     </row>
     <row r="32" spans="1:19" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>51</v>
+        <v>20</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>21</v>
@@ -2505,13 +2493,13 @@
         <v>1</v>
       </c>
       <c r="G32" s="2">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="H32" s="1" t="s">
         <v>2</v>
       </c>
       <c r="I32" s="3">
-        <v>26502.63</v>
+        <v>159822.76</v>
       </c>
       <c r="J32" s="2">
         <v>0</v>
@@ -2546,7 +2534,7 @@
     </row>
     <row r="33" spans="1:19" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>51</v>
+        <v>27</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>21</v>
@@ -2564,13 +2552,13 @@
         <v>1</v>
       </c>
       <c r="G33" s="2">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H33" s="1" t="s">
         <v>2</v>
       </c>
       <c r="I33" s="3">
-        <v>64931.43</v>
+        <v>0</v>
       </c>
       <c r="J33" s="2">
         <v>0</v>
@@ -2605,7 +2593,7 @@
     </row>
     <row r="34" spans="1:19" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>21</v>
@@ -2623,13 +2611,13 @@
         <v>1</v>
       </c>
       <c r="G34" s="2">
-        <v>2</v>
+        <v>43</v>
       </c>
       <c r="H34" s="1" t="s">
         <v>2</v>
       </c>
       <c r="I34" s="3">
-        <v>12294.06</v>
+        <v>0</v>
       </c>
       <c r="J34" s="2">
         <v>0</v>
@@ -2664,7 +2652,7 @@
     </row>
     <row r="35" spans="1:19" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>21</v>
@@ -2682,13 +2670,13 @@
         <v>1</v>
       </c>
       <c r="G35" s="2">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="H35" s="1" t="s">
         <v>2</v>
       </c>
       <c r="I35" s="3">
-        <v>159822.76</v>
+        <v>0</v>
       </c>
       <c r="J35" s="2">
         <v>0</v>
@@ -2723,7 +2711,7 @@
     </row>
     <row r="36" spans="1:19" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>27</v>
+        <v>51</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>21</v>
@@ -2741,7 +2729,7 @@
         <v>1</v>
       </c>
       <c r="G36" s="2">
-        <v>50</v>
+        <v>7</v>
       </c>
       <c r="H36" s="1" t="s">
         <v>2</v>
@@ -2782,7 +2770,7 @@
     </row>
     <row r="37" spans="1:19" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>27</v>
+        <v>63</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>21</v>
@@ -2800,13 +2788,13 @@
         <v>1</v>
       </c>
       <c r="G37" s="2">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="H37" s="1" t="s">
         <v>2</v>
       </c>
       <c r="I37" s="3">
-        <v>0</v>
+        <v>322332.88</v>
       </c>
       <c r="J37" s="2">
         <v>0</v>
@@ -2841,7 +2829,7 @@
     </row>
     <row r="38" spans="1:19" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>21</v>
@@ -2859,13 +2847,13 @@
         <v>1</v>
       </c>
       <c r="G38" s="2">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="H38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="I38" s="3">
-        <v>0</v>
+        <v>138945.97</v>
       </c>
       <c r="J38" s="2">
         <v>0</v>
@@ -3136,7 +3124,7 @@
     </row>
     <row r="43" spans="1:19" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>21</v>
@@ -3195,7 +3183,7 @@
     </row>
     <row r="44" spans="1:19" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>21</v>
@@ -3213,13 +3201,13 @@
         <v>1</v>
       </c>
       <c r="G44" s="2">
-        <v>27</v>
+        <v>2</v>
       </c>
       <c r="H44" s="1" t="s">
         <v>2</v>
       </c>
       <c r="I44" s="3">
-        <v>229469.75</v>
+        <v>16997.759999999998</v>
       </c>
       <c r="J44" s="2">
         <v>0</v>
@@ -3254,7 +3242,7 @@
     </row>
     <row r="45" spans="1:19" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>21</v>
@@ -3313,7 +3301,7 @@
     </row>
     <row r="46" spans="1:19" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>21</v>
@@ -3331,13 +3319,13 @@
         <v>1</v>
       </c>
       <c r="G46" s="2">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="H46" s="1" t="s">
         <v>2</v>
       </c>
       <c r="I46" s="3">
-        <v>125226.19</v>
+        <v>104343.85</v>
       </c>
       <c r="J46" s="2">
         <v>0</v>
@@ -3372,7 +3360,7 @@
     </row>
     <row r="47" spans="1:19" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>21</v>
@@ -3396,7 +3384,7 @@
         <v>2</v>
       </c>
       <c r="I47" s="3">
-        <v>104355.16</v>
+        <v>104343.85</v>
       </c>
       <c r="J47" s="2">
         <v>0</v>
@@ -3667,7 +3655,7 @@
     </row>
     <row r="52" spans="1:19" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>21</v>
@@ -3785,7 +3773,7 @@
     </row>
     <row r="54" spans="1:19" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>21</v>
@@ -3803,13 +3791,13 @@
         <v>1</v>
       </c>
       <c r="G54" s="2">
-        <v>2</v>
+        <v>52</v>
       </c>
       <c r="H54" s="1" t="s">
         <v>2</v>
       </c>
       <c r="I54" s="3">
-        <v>376920.88</v>
+        <v>13456.28</v>
       </c>
       <c r="J54" s="2">
         <v>0</v>
@@ -3844,7 +3832,7 @@
     </row>
     <row r="55" spans="1:19" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>21</v>
@@ -3862,13 +3850,13 @@
         <v>1</v>
       </c>
       <c r="G55" s="2">
-        <v>62</v>
+        <v>40</v>
       </c>
       <c r="H55" s="1" t="s">
         <v>2</v>
       </c>
       <c r="I55" s="3">
-        <v>16044.03</v>
+        <v>10350.99</v>
       </c>
       <c r="J55" s="2">
         <v>0</v>
@@ -3903,7 +3891,7 @@
     </row>
     <row r="56" spans="1:19" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>21</v>
@@ -3921,13 +3909,13 @@
         <v>1</v>
       </c>
       <c r="G56" s="2">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="H56" s="1" t="s">
         <v>2</v>
       </c>
       <c r="I56" s="3">
-        <v>10350.99</v>
+        <v>2439.75</v>
       </c>
       <c r="J56" s="2">
         <v>0</v>
@@ -3961,356 +3949,61 @@
       </c>
     </row>
     <row r="57" spans="1:19" ht="14.4" x14ac:dyDescent="0.25">
-      <c r="A57" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="B57" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C57" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D57" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="E57" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="F57" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="G57" s="2">
-        <v>12</v>
-      </c>
-      <c r="H57" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="I57" s="3">
-        <v>2439.75</v>
-      </c>
-      <c r="J57" s="2">
-        <v>0</v>
-      </c>
-      <c r="K57" s="3">
-        <v>0</v>
-      </c>
-      <c r="L57" s="2">
-        <v>0</v>
-      </c>
-      <c r="M57" s="3">
-        <v>0</v>
-      </c>
-      <c r="N57" s="2">
-        <v>0</v>
-      </c>
-      <c r="O57" s="3">
-        <v>0</v>
-      </c>
-      <c r="P57" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q57" s="3">
-        <v>0</v>
-      </c>
-      <c r="R57" s="2">
-        <v>0</v>
-      </c>
-      <c r="S57" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" spans="1:19" ht="14.4" x14ac:dyDescent="0.25">
-      <c r="A58" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="B58" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C58" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D58" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="E58" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="F58" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="G58" s="2">
-        <v>2</v>
-      </c>
-      <c r="H58" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="I58" s="3">
-        <v>0</v>
-      </c>
-      <c r="J58" s="2">
-        <v>0</v>
-      </c>
-      <c r="K58" s="3">
-        <v>0</v>
-      </c>
-      <c r="L58" s="2">
-        <v>0</v>
-      </c>
-      <c r="M58" s="3">
-        <v>0</v>
-      </c>
-      <c r="N58" s="2">
-        <v>0</v>
-      </c>
-      <c r="O58" s="3">
-        <v>0</v>
-      </c>
-      <c r="P58" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q58" s="3">
-        <v>0</v>
-      </c>
-      <c r="R58" s="2">
-        <v>0</v>
-      </c>
-      <c r="S58" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="1:19" ht="14.4" x14ac:dyDescent="0.25">
-      <c r="A59" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="B59" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C59" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D59" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="E59" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="F59" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="G59" s="2">
-        <v>2</v>
-      </c>
-      <c r="H59" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="I59" s="3">
-        <v>0</v>
-      </c>
-      <c r="J59" s="2">
-        <v>0</v>
-      </c>
-      <c r="K59" s="3">
-        <v>0</v>
-      </c>
-      <c r="L59" s="2">
-        <v>0</v>
-      </c>
-      <c r="M59" s="3">
-        <v>0</v>
-      </c>
-      <c r="N59" s="2">
-        <v>0</v>
-      </c>
-      <c r="O59" s="3">
-        <v>0</v>
-      </c>
-      <c r="P59" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q59" s="3">
-        <v>0</v>
-      </c>
-      <c r="R59" s="2">
-        <v>0</v>
-      </c>
-      <c r="S59" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60" spans="1:19" ht="14.4" x14ac:dyDescent="0.25">
-      <c r="A60" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="B60" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C60" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D60" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="E60" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="F60" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="G60" s="2">
-        <v>2</v>
-      </c>
-      <c r="H60" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="I60" s="3">
-        <v>0</v>
-      </c>
-      <c r="J60" s="2">
-        <v>0</v>
-      </c>
-      <c r="K60" s="3">
-        <v>0</v>
-      </c>
-      <c r="L60" s="2">
-        <v>0</v>
-      </c>
-      <c r="M60" s="3">
-        <v>0</v>
-      </c>
-      <c r="N60" s="2">
-        <v>0</v>
-      </c>
-      <c r="O60" s="3">
-        <v>0</v>
-      </c>
-      <c r="P60" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q60" s="3">
-        <v>0</v>
-      </c>
-      <c r="R60" s="2">
-        <v>0</v>
-      </c>
-      <c r="S60" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61" spans="1:19" ht="14.4" x14ac:dyDescent="0.25">
-      <c r="A61" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="B61" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C61" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D61" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="E61" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="F61" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="G61" s="2">
-        <v>2</v>
-      </c>
-      <c r="H61" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="I61" s="3">
-        <v>0</v>
-      </c>
-      <c r="J61" s="2">
-        <v>0</v>
-      </c>
-      <c r="K61" s="3">
-        <v>0</v>
-      </c>
-      <c r="L61" s="2">
-        <v>0</v>
-      </c>
-      <c r="M61" s="3">
-        <v>0</v>
-      </c>
-      <c r="N61" s="2">
-        <v>0</v>
-      </c>
-      <c r="O61" s="3">
-        <v>0</v>
-      </c>
-      <c r="P61" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q61" s="3">
-        <v>0</v>
-      </c>
-      <c r="R61" s="2">
-        <v>0</v>
-      </c>
-      <c r="S61" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="1:19" ht="14.4" x14ac:dyDescent="0.25">
-      <c r="A62" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B62" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="C62" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="D62" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="E62" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="F62" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="G62" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="H62" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="I62" s="5">
-        <v>7087950.3799999999</v>
-      </c>
-      <c r="J62" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="K62" s="5">
-        <v>0</v>
-      </c>
-      <c r="L62" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="M62" s="5">
-        <v>0</v>
-      </c>
-      <c r="N62" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="O62" s="5">
-        <v>0</v>
-      </c>
-      <c r="P62" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="Q62" s="5">
-        <v>0</v>
-      </c>
-      <c r="R62" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="S62" s="5">
+      <c r="A57" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B57" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C57" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="D57" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="E57" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="F57" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="G57" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="H57" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="I57" s="5">
+        <v>6269485.3799999999</v>
+      </c>
+      <c r="J57" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="K57" s="5">
+        <v>0</v>
+      </c>
+      <c r="L57" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="M57" s="5">
+        <v>0</v>
+      </c>
+      <c r="N57" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="O57" s="5">
+        <v>0</v>
+      </c>
+      <c r="P57" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q57" s="5">
+        <v>0</v>
+      </c>
+      <c r="R57" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="S57" s="5">
         <v>0</v>
       </c>
     </row>
